--- a/基本設計/23_学員Reviewテスト管理.xlsx
+++ b/基本設計/23_学員Reviewテスト管理.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R8ddfb8d865ea49b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R16899dbaa53a4a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_詳細設計成果物" sheetId="42" r:id="Rbe34bd07c23b4427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_Reviewチェック" sheetId="43" r:id="R40363c5697524eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_Codingチェック" sheetId="44" r:id="R9410cbf0c6c94c08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_単体テスト証跡" sheetId="45" r:id="R5484e41486134346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_レビュー記録" sheetId="46" r:id="R62148e7b6eb04a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_受入条件" sheetId="47" r:id="Rd0f311727c084660"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_設計注意事項" sheetId="48" r:id="R1cb1e615cfb645d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_基本設計完了判定" sheetId="49" r:id="Rf18c643f49bc4540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_結合テスト方針" sheetId="50" r:id="Rd3638f92e287475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R5b87887782e04d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R673bf6cf70894e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_詳細設計成果物" sheetId="42" r:id="Rb5a9930ba0584c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_Reviewチェック" sheetId="43" r:id="R214ae1a6840c48a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_Codingチェック" sheetId="44" r:id="R23a349dc9b7a420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_単体テスト証跡" sheetId="45" r:id="Rc419a5c09f334a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_レビュー記録" sheetId="46" r:id="R09a3ca1f99d44991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_受入条件" sheetId="47" r:id="R48182781b283445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_設計注意事項" sheetId="48" r:id="Rd264bb1ae48c48fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_基本設計完了判定" sheetId="49" r:id="Rffe962790d7a42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_結合テスト方針" sheetId="50" r:id="R77bfeb2b4894488f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1099,10 +1099,7 @@
       <x:c r="F16" s="135"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1117,25 +1114,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="178" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="178"/>
-      <x:c r="D19" s="178"/>
-      <x:c r="E19" s="178"/>
-      <x:c r="F19" s="178"/>
-      <x:c r="G19" s="178"/>
-      <x:c r="H19" s="178"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="178"/>
-      <x:c r="C20" s="178"/>
-      <x:c r="D20" s="178"/>
-      <x:c r="E20" s="178"/>
-      <x:c r="F20" s="178"/>
-      <x:c r="G20" s="178"/>
-      <x:c r="H20" s="178"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="178"/>
